--- a/trust/ValueSet-Participants-DEV.xlsx
+++ b/trust/ValueSet-Participants-DEV.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.0</t>
+    <t>1.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-27T08:38:34+00:00</t>
+    <t>2026-02-11T14:17:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/trust/ValueSet-Participants-DEV.xlsx
+++ b/trust/ValueSet-Participants-DEV.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.4.0</t>
+    <t>1.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T14:17:30+00:00</t>
+    <t>2026-04-27T07:32:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/trust/ValueSet-Participants-DEV.xlsx
+++ b/trust/ValueSet-Participants-DEV.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.5.0</t>
+    <t>1.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-27T07:32:49+00:00</t>
+    <t>2026-07-03T08:24:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/trust/ValueSet-Participants-DEV.xlsx
+++ b/trust/ValueSet-Participants-DEV.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-03T08:24:29+00:00</t>
+    <t>2026-07-06T11:52:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/trust/ValueSet-Participants-DEV.xlsx
+++ b/trust/ValueSet-Participants-DEV.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.6.0</t>
+    <t>1.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T11:52:41+00:00</t>
+    <t>2026-07-30T11:57:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/trust/ValueSet-Participants-DEV.xlsx
+++ b/trust/ValueSet-Participants-DEV.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="94">
   <si>
     <t>Property</t>
   </si>
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.7.0</t>
+    <t>1.7.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T11:57:48+00:00</t>
+    <t>2026-08-27T05:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -122,6 +122,9 @@
     <t>AND</t>
   </si>
   <si>
+    <t>ARE</t>
+  </si>
+  <si>
     <t>ARG</t>
   </si>
   <si>
@@ -134,6 +137,9 @@
     <t>BLZ</t>
   </si>
   <si>
+    <t>BOL</t>
+  </si>
+  <si>
     <t>BRA</t>
   </si>
   <si>
@@ -170,9 +176,15 @@
     <t>IDN</t>
   </si>
   <si>
+    <t>JAM</t>
+  </si>
+  <si>
     <t>LVA</t>
   </si>
   <si>
+    <t>NIC</t>
+  </si>
+  <si>
     <t>OMN</t>
   </si>
   <si>
@@ -203,6 +215,9 @@
     <t>TGO</t>
   </si>
   <si>
+    <t>TTO</t>
+  </si>
+  <si>
     <t>URY</t>
   </si>
   <si>
@@ -212,6 +227,9 @@
     <t>http://smart.who.int/refmart/CodeSystems/REF_COUNTRY</t>
   </si>
   <si>
+    <t>IOM</t>
+  </si>
+  <si>
     <t>XCL</t>
   </si>
   <si>
@@ -251,16 +269,28 @@
     <t>XXK</t>
   </si>
   <si>
+    <t>XXN</t>
+  </si>
+  <si>
     <t>XXO</t>
   </si>
   <si>
     <t>XXP</t>
   </si>
   <si>
+    <t>XXQ</t>
+  </si>
+  <si>
+    <t>XXT</t>
+  </si>
+  <si>
     <t>XXU</t>
   </si>
   <si>
     <t>XXV</t>
+  </si>
+  <si>
+    <t>XXW</t>
   </si>
   <si>
     <t>XXX</t>
@@ -570,7 +600,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -767,18 +797,48 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>30</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="B32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="B33" s="2"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B34" s="2"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="B35" s="2"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B36" s="2"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
         <v>31</v>
       </c>
-      <c r="B33" t="s" s="2">
-        <v>64</v>
+      <c r="B38" t="s" s="2">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -788,7 +848,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -805,137 +865,167 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>30</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="B22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="B23" s="2"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="B24" s="2"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="B25" s="2"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="B26" s="2"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
         <v>31</v>
       </c>
-      <c r="B23" t="s" s="2">
+      <c r="B28" t="s" s="2">
         <v>32</v>
       </c>
     </row>

--- a/trust/ValueSet-Participants-DEV.xlsx
+++ b/trust/ValueSet-Participants-DEV.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.7.1</t>
+    <t>1.7.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T05:52:17+00:00</t>
+    <t>2026-09-03T12:39:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
